--- a/data/trans_orig/RUIDO_1-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del ruido en 2023</t>
+          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del ruido en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1388</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5385</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1325</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4009</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4052</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1325</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4669</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>8097</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,62 +878,62 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>7217</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1445</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>6958</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -956,97 +956,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1388</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3579</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>631</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3171</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>3214</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>3652</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1388</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1129</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3530</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>973</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8291</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>4856</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,62 +1330,62 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>5305</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>961</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>4837</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>705</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>7833</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11643</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>604</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>8242</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1634,12 +1634,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14626</t>
+          <t>15251</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15320</t>
+          <t>15138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12437</t>
+          <t>11775</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26365</t>
+          <t>26165</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5453</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15875</t>
+          <t>15967</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13886</t>
+          <t>13836</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30618</t>
+          <t>30203</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21655</t>
+          <t>21998</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40966</t>
+          <t>41487</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>218294</t>
+          <t>217875</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>236627</t>
+          <t>236128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>333062</t>
+          <t>333216</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>351909</t>
+          <t>352110</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>557068</t>
+          <t>558567</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>583237</t>
+          <t>584786</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,88%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>10255</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7119</t>
+          <t>6833</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,42 +2145,42 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>6820</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2896</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>13531</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>0,59%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>6820</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>2972</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>13663</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13596</t>
+          <t>14168</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17727</t>
+          <t>17894</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>6038</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -2429,97 +2429,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1942</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6337</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>1066</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5479</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5869</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5185</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16129</t>
+          <t>15629</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2577,12 +2577,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13935</t>
+          <t>14057</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>8982</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24783</t>
+          <t>25583</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -2655,12 +2655,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6241</t>
+          <t>6218</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33992</t>
+          <t>32046</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>10971</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10063</t>
+          <t>10482</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38111</t>
+          <t>38183</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12725</t>
+          <t>11731</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43608</t>
+          <t>42988</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21230</t>
+          <t>20679</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>177515</t>
+          <t>204640</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42578</t>
+          <t>41491</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>219368</t>
+          <t>182872</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -2881,12 +2881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13557</t>
+          <t>14128</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>36892</t>
+          <t>36956</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18564</t>
+          <t>18902</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>22886</t>
+          <t>22850</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>51434</t>
+          <t>49336</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>51959</t>
+          <t>53178</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>99518</t>
+          <t>99908</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27360</t>
+          <t>25937</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>62142</t>
+          <t>63347</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>86901</t>
+          <t>83993</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>149116</t>
+          <t>149622</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>92265</t>
+          <t>93944</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>137753</t>
+          <t>134256</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>64470</t>
+          <t>63601</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>147359</t>
+          <t>148697</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>161387</t>
+          <t>164232</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>264394</t>
+          <t>263000</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>777004</t>
+          <t>779399</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>847824</t>
+          <t>846015</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>874688</t>
+          <t>865249</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1051148</t>
+          <t>1051423</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1675969</t>
+          <t>1675054</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1887546</t>
+          <t>1903752</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,6%</t>
         </is>
       </c>
     </row>
@@ -3450,12 +3450,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12099</t>
+          <t>13586</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>891</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9521</t>
+          <t>8662</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>17271</t>
+          <t>16634</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -3563,12 +3563,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10874</t>
+          <t>11966</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12202</t>
+          <t>11595</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18126</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8625</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -3789,97 +3789,97 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>1416</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>1786</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
         <is>
           <t>1416</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="S31" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>4968</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>4979</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>1416</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>4751</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -3902,12 +3902,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11235</t>
+          <t>12226</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>2586</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12642</t>
+          <t>12296</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>19358</t>
+          <t>19741</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -4015,12 +4015,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>12344</t>
+          <t>12222</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>10099</t>
+          <t>9683</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>5437</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>18370</t>
+          <t>18913</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11844</t>
+          <t>11448</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4143,12 +4143,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6060</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>21475</t>
+          <t>21979</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>10463</t>
+          <t>10517</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>27054</t>
+          <t>28126</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -4241,12 +4241,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3677</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14979</t>
+          <t>15640</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8683</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>6793</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>19505</t>
+          <t>19921</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7808</t>
+          <t>7883</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>28822</t>
+          <t>27207</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>11418</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>22904</t>
+          <t>23007</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>22239</t>
+          <t>21949</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>43675</t>
+          <t>44466</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>53635</t>
+          <t>54318</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>81855</t>
+          <t>83277</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>35640</t>
+          <t>35036</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>54528</t>
+          <t>53920</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>95807</t>
+          <t>96254</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>130156</t>
+          <t>129675</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>189125</t>
+          <t>187495</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>226345</t>
+          <t>224918</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>208881</t>
+          <t>209408</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>236033</t>
+          <t>238040</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>406724</t>
+          <t>407101</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>452942</t>
+          <t>452495</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,0%</t>
         </is>
       </c>
     </row>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>18530</t>
+          <t>18318</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4825,82 +4825,82 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>7360</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>3315</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>13752</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>9978</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>27583</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>7360</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>3618</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>13181</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>16426</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>9788</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>26768</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -4923,12 +4923,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>22258</t>
+          <t>22108</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>4681</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>15929</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>14388</t>
+          <t>14466</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>32851</t>
+          <t>32565</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>628</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>10544</t>
+          <t>10169</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>12336</t>
+          <t>13191</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -5149,12 +5149,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5164,12 +5164,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>8365</t>
+          <t>7479</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -5262,12 +5262,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>8410</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>23688</t>
+          <t>25479</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5277,12 +5277,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>8506</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>23159</t>
+          <t>23335</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>19852</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>41429</t>
+          <t>40914</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -5375,12 +5375,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>11198</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>42382</t>
+          <t>39259</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5390,12 +5390,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>17267</t>
+          <t>17757</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>18635</t>
+          <t>17784</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>49700</t>
+          <t>48712</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -5488,12 +5488,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>19697</t>
+          <t>18169</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>51416</t>
+          <t>51068</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5503,12 +5503,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>36550</t>
+          <t>35629</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>226890</t>
+          <t>198334</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>66605</t>
+          <t>64352</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>236656</t>
+          <t>242999</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -5601,12 +5601,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>22385</t>
+          <t>22112</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>49006</t>
+          <t>47342</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>9760</t>
+          <t>10432</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>24104</t>
+          <t>24938</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>35946</t>
+          <t>34967</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>67786</t>
+          <t>67362</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>70458</t>
+          <t>71844</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>121853</t>
+          <t>121019</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5729,12 +5729,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>50273</t>
+          <t>50913</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>89377</t>
+          <t>90641</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>133894</t>
+          <t>132213</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>198514</t>
+          <t>203613</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -5827,12 +5827,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>165659</t>
+          <t>164447</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>217356</t>
+          <t>217354</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>125976</t>
+          <t>129952</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>214138</t>
+          <t>213704</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>302058</t>
+          <t>296011</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>415015</t>
+          <t>414415</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1208685</t>
+          <t>1206035</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1286556</t>
+          <t>1289230</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1428956</t>
+          <t>1430633</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1628198</t>
+          <t>1631355</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>2675239</t>
+          <t>2669927</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>2895720</t>
+          <t>2912161</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_1-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Estudios-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>8428</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>707</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>707</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6737</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>808</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7733</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>912</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>4460</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>912</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -1403,32 +1403,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>658</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7833</t>
+          <t>7883</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,27 +1438,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6060</t>
+          <t>6657</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5668</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>11767</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -1516,22 +1516,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>704</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7050</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3664</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8242</t>
+          <t>8767</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -1629,32 +1629,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>10781</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>20467</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1664,32 +1664,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15138</t>
+          <t>16056</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,32 +1699,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>17998</t>
+          <t>21626</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11775</t>
+          <t>14134</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26165</t>
+          <t>31775</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>9868</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15967</t>
+          <t>16466</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1777,32 +1777,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20305</t>
+          <t>22233</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13836</t>
+          <t>15443</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30203</t>
+          <t>33919</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,32 +1812,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>29625</t>
+          <t>32101</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21998</t>
+          <t>23320</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41487</t>
+          <t>43631</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -1855,69 +1855,69 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>228403</t>
+          <t>261300</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>217875</t>
+          <t>248335</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>236128</t>
+          <t>270953</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>92,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>377908</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>366552</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>387075</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>90,31%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>87,6%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>92,5%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>662</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>343890</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>333216</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>352110</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>90,21%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>87,41%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>92,37%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>981</t>
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>572293</t>
+          <t>639208</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>558567</t>
+          <t>624564</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>584786</t>
+          <t>653186</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,92%</t>
         </is>
       </c>
     </row>
@@ -1968,17 +1968,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>255267</t>
+          <t>292160</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>255267</t>
+          <t>292160</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>255267</t>
+          <t>292160</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>381214</t>
+          <t>418450</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>381214</t>
+          <t>418450</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>381214</t>
+          <t>418450</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2038,17 +2038,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>636481</t>
+          <t>710610</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>636481</t>
+          <t>710610</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>636481</t>
+          <t>710610</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>11198</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>710</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13531</t>
+          <t>13837</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -2198,32 +2198,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6775</t>
+          <t>9026</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14168</t>
+          <t>19209</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>7614</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>10227</t>
+          <t>12587</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17894</t>
+          <t>23456</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>692</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6038</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -2537,22 +2537,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15629</t>
+          <t>15766</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2572,32 +2572,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7613</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14057</t>
+          <t>15805</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2607,32 +2607,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>15773</t>
+          <t>17384</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8982</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25583</t>
+          <t>26378</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -2650,32 +2650,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13793</t>
+          <t>13124</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6218</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>32046</t>
+          <t>33409</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2685,32 +2685,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10971</t>
+          <t>11214</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2720,32 +2720,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>19167</t>
+          <t>18559</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10482</t>
+          <t>10512</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38183</t>
+          <t>38851</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -2763,32 +2763,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>22483</t>
+          <t>24398</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11731</t>
+          <t>13541</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42988</t>
+          <t>42886</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2798,32 +2798,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>59567</t>
+          <t>30427</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20679</t>
+          <t>20738</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>204640</t>
+          <t>47926</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,32 +2833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>82050</t>
+          <t>54825</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41491</t>
+          <t>37826</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>182872</t>
+          <t>77492</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -2876,32 +2876,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>22990</t>
+          <t>23600</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14128</t>
+          <t>13856</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>36956</t>
+          <t>38232</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>11759</t>
+          <t>12893</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>8059</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18902</t>
+          <t>19360</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>34749</t>
+          <t>36492</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>22850</t>
+          <t>25885</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>49336</t>
+          <t>51676</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -2989,32 +2989,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>69947</t>
+          <t>71943</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>53178</t>
+          <t>52267</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>99908</t>
+          <t>97289</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3024,32 +3024,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>47144</t>
+          <t>55390</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25937</t>
+          <t>42854</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>63347</t>
+          <t>68116</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>117091</t>
+          <t>127333</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>83993</t>
+          <t>104939</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>149622</t>
+          <t>153652</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -3102,32 +3102,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>111801</t>
+          <t>119300</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>93944</t>
+          <t>99548</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>134256</t>
+          <t>141189</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3137,32 +3137,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>116398</t>
+          <t>126397</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>63601</t>
+          <t>109224</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>148697</t>
+          <t>148414</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,32 +3172,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>228199</t>
+          <t>245697</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>164232</t>
+          <t>217042</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>263000</t>
+          <t>275023</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -3215,32 +3215,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>813869</t>
+          <t>885313</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>779399</t>
+          <t>847679</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>846015</t>
+          <t>916851</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3250,32 +3250,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>946313</t>
+          <t>824392</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>865249</t>
+          <t>797648</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1051423</t>
+          <t>847394</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3285,32 +3285,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1760182</t>
+          <t>1709705</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1675054</t>
+          <t>1662522</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1903752</t>
+          <t>1747688</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>78,28%</t>
         </is>
       </c>
     </row>
@@ -3328,17 +3328,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1075088</t>
+          <t>1160277</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1075088</t>
+          <t>1160277</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1075088</t>
+          <t>1160277</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1202013</t>
+          <t>1072269</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1202013</t>
+          <t>1072269</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1202013</t>
+          <t>1072269</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,17 +3398,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2277101</t>
+          <t>2232547</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2277101</t>
+          <t>2232547</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2277101</t>
+          <t>2232547</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3445,102 +3445,102 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>4924</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13586</t>
+          <t>15682</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>3496</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>883</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>9269</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>10796</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>5355</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>20842</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>3357</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>8662</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>8281</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>3797</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>16634</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -3558,32 +3558,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4741</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11966</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3593,32 +3593,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>12007</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3628,32 +3628,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>10573</t>
+          <t>11755</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>19364</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>6032</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3741,32 +3741,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9619</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -3897,32 +3897,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>4649</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>13693</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3932,22 +3932,22 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12296</t>
+          <t>12590</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3967,32 +3967,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>10488</t>
+          <t>11366</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5486</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>19741</t>
+          <t>21018</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -4010,32 +4010,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>12222</t>
+          <t>12244</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4045,32 +4045,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>10844</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4080,32 +4080,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10172</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>18913</t>
+          <t>18647</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -4123,32 +4123,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11448</t>
+          <t>13399</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4158,32 +4158,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>12013</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>21979</t>
+          <t>21456</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4193,22 +4193,22 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>17413</t>
+          <t>19002</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>10517</t>
+          <t>11611</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>28126</t>
+          <t>30049</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -4236,32 +4236,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>7695</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3677</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15640</t>
+          <t>15505</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4271,22 +4271,22 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t>9200</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4306,32 +4306,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>11772</t>
+          <t>12847</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>6793</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>19921</t>
+          <t>20375</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -4349,32 +4349,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>14688</t>
+          <t>16940</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7883</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>27207</t>
+          <t>30227</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4384,32 +4384,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>16537</t>
+          <t>21305</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>10884</t>
+          <t>14835</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>23007</t>
+          <t>29531</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4419,32 +4419,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>31225</t>
+          <t>38245</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>21949</t>
+          <t>27935</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>44466</t>
+          <t>53325</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -4462,32 +4462,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>67821</t>
+          <t>72569</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>54318</t>
+          <t>59178</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>83277</t>
+          <t>88699</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4497,32 +4497,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>44268</t>
+          <t>47777</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>35036</t>
+          <t>38291</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>53920</t>
+          <t>58071</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4532,32 +4532,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>112089</t>
+          <t>120346</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>96254</t>
+          <t>104020</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>129675</t>
+          <t>139860</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -4575,32 +4575,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>206930</t>
+          <t>216773</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>187495</t>
+          <t>196940</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>224918</t>
+          <t>234143</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4610,32 +4610,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>223041</t>
+          <t>253496</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>209408</t>
+          <t>237158</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>238040</t>
+          <t>267805</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4645,32 +4645,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>429972</t>
+          <t>470269</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>407101</t>
+          <t>445120</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>452495</t>
+          <t>493698</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,51%</t>
         </is>
       </c>
     </row>
@@ -4688,17 +4688,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>323814</t>
+          <t>346652</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>323814</t>
+          <t>346652</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>323814</t>
+          <t>346652</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4723,17 +4723,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>322646</t>
+          <t>363628</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>322646</t>
+          <t>363628</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>322646</t>
+          <t>363628</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4758,17 +4758,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>646461</t>
+          <t>710280</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>646461</t>
+          <t>710280</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>646461</t>
+          <t>710280</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4805,32 +4805,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>9066</t>
+          <t>11575</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>18318</t>
+          <t>20347</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4840,32 +4840,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>13752</t>
+          <t>14254</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4875,32 +4875,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>16426</t>
+          <t>19190</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>9978</t>
+          <t>11387</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>27583</t>
+          <t>30246</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -4918,32 +4918,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>15512</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>6628</t>
+          <t>9031</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>22108</t>
+          <t>27175</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4953,32 +4953,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>9284</t>
+          <t>10341</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>15296</t>
+          <t>16824</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4988,32 +4988,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>22245</t>
+          <t>25853</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>14466</t>
+          <t>17466</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>32565</t>
+          <t>37484</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -5031,32 +5031,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>11899</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5066,32 +5066,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>695</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>10169</t>
+          <t>8611</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5101,32 +5101,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>13191</t>
+          <t>13833</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -5179,32 +5179,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>717</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>7864</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5214,17 +5214,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>711</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7479</t>
+          <t>7164</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -5257,32 +5257,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>15378</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>8216</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>25479</t>
+          <t>25286</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5292,32 +5292,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>16609</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>23335</t>
+          <t>25203</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5327,32 +5327,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>29132</t>
+          <t>31987</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>22898</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>40914</t>
+          <t>44341</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -5370,32 +5370,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>20097</t>
+          <t>19203</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10587</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>39259</t>
+          <t>36250</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5405,67 +5405,67 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10439</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>5714</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>17757</t>
+          <t>16854</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>29642</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>19698</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>45429</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
           <t>0,54%</t>
         </is>
       </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>30308</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>17784</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>48712</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -5483,27 +5483,27 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>30922</t>
+          <t>34281</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>18169</t>
+          <t>21625</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>51068</t>
+          <t>55672</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -5518,32 +5518,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>74209</t>
+          <t>45511</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>35629</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>198334</t>
+          <t>62233</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5553,32 +5553,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>105131</t>
+          <t>79792</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>64352</t>
+          <t>60704</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>242999</t>
+          <t>104375</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -5596,32 +5596,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>33180</t>
+          <t>34404</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>22112</t>
+          <t>23496</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>47342</t>
+          <t>52049</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5631,32 +5631,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>18881</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>10432</t>
+          <t>12851</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>24938</t>
+          <t>26903</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5666,32 +5666,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>50184</t>
+          <t>53286</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>34967</t>
+          <t>40240</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>67362</t>
+          <t>70550</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -5709,32 +5709,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>92646</t>
+          <t>99664</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>71844</t>
+          <t>79103</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>121019</t>
+          <t>128488</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5744,32 +5744,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>73667</t>
+          <t>87540</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>50913</t>
+          <t>73145</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>90641</t>
+          <t>104648</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5779,32 +5779,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>166314</t>
+          <t>187204</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>132213</t>
+          <t>160861</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>203613</t>
+          <t>218127</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -5822,32 +5822,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>188942</t>
+          <t>201737</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>164447</t>
+          <t>173960</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>217354</t>
+          <t>229139</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5857,32 +5857,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>180971</t>
+          <t>196407</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>129952</t>
+          <t>172798</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>213704</t>
+          <t>221477</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5892,32 +5892,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>369913</t>
+          <t>398144</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>296011</t>
+          <t>365438</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>414415</t>
+          <t>434544</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -5935,32 +5935,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>1249203</t>
+          <t>1363386</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1206035</t>
+          <t>1320228</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1289230</t>
+          <t>1400284</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5970,32 +5970,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>1513243</t>
+          <t>1455796</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1430633</t>
+          <t>1424310</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1631355</t>
+          <t>1485808</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6005,32 +6005,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>2762446</t>
+          <t>2819183</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>2669927</t>
+          <t>2769695</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>2912161</t>
+          <t>2868857</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>78,52%</t>
         </is>
       </c>
     </row>
@@ -6048,17 +6048,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>1654169</t>
+          <t>1799089</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>1654169</t>
+          <t>1799089</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>1654169</t>
+          <t>1799089</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6083,17 +6083,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>1905873</t>
+          <t>1854348</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>1905873</t>
+          <t>1854348</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>1905873</t>
+          <t>1854348</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6118,17 +6118,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>3560042</t>
+          <t>3653437</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>3560042</t>
+          <t>3653437</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>3560042</t>
+          <t>3653437</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">

--- a/data/trans_orig/RUIDO_1-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del ruido en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del ruido en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
